--- a/KPI_Workbook.xlsx
+++ b/KPI_Workbook.xlsx
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>46137.3094985277</v>
+        <v>46137.31100720354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>46137.30949851077</v>
+        <v>46137.31100718575</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>

--- a/KPI_Workbook.xlsx
+++ b/KPI_Workbook.xlsx
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>46137.31100720354</v>
+        <v>46137.32097220042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>46137.31100718575</v>
+        <v>46137.32097217493</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>

--- a/KPI_Workbook.xlsx
+++ b/KPI_Workbook.xlsx
@@ -2979,7 +2979,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="62" t="n">
-        <v>46137.32682931781</v>
+        <v>46137.33146576225</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="62" t="n">
-        <v>46137.32682934483</v>
+        <v>46137.33146578698</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/KPI_Workbook.xlsx
+++ b/KPI_Workbook.xlsx
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1688,48 +1688,42 @@
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="52" t="inlineStr">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="52" t="inlineStr">
         <is>
           <t>&gt;&gt; IN_PACKED</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="52" t="inlineStr">
+      <c r="D25" s="52" t="inlineStr">
         <is>
           <t>&gt;&gt; IN_HRP</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="53" t="inlineStr">
+      <c r="F25" s="53" t="inlineStr">
         <is>
           <t>&gt;&gt; IN_SHIPPED_LPNS</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="53" t="inlineStr">
+      <c r="H25" s="53" t="inlineStr">
         <is>
           <t>&gt;&gt; IN_STAFFING</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="54" t="inlineStr">
+      <c r="J25" s="54" t="inlineStr">
         <is>
           <t>&gt;&gt; T_DISPATCH_KPI</t>
         </is>
       </c>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="54" t="inlineStr">
+      <c r="L25" s="54" t="inlineStr">
         <is>
           <t>&gt;&gt; DATA_QUALITY</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="55" t="inlineStr">
+      <c r="N25" s="55" t="inlineStr">
         <is>
           <t>&gt;&gt; HISTORY</t>
         </is>
       </c>
-      <c r="N25" s="5" t="n"/>
     </row>
     <row r="26" ht="8" customHeight="1">
       <c r="A26" s="5" t="n"/>
@@ -1975,15 +1969,19 @@
       <c r="N40" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="40">
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="J6:L8"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A24:N24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="N25:O25"/>
     <mergeCell ref="B10:D12"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="H25:I25"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="F28:H28"/>
     <mergeCell ref="B6:D8"/>
@@ -1993,11 +1991,14 @@
     <mergeCell ref="J21:L21"/>
     <mergeCell ref="A27:N27"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
     <mergeCell ref="F10:H12"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="A14:N14"/>
     <mergeCell ref="J29:L29"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="J28:L28"/>
     <mergeCell ref="A4:N4"/>
@@ -2026,13 +2027,13 @@
     <cfRule type="containsText" priority="9" operator="containsText" dxfId="2" text="Red"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2979,7 +2980,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="62" t="n">
-        <v>46137.33146576225</v>
+        <v>46137.35423373283</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -3152,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="62" t="n">
-        <v>46137.33146578698</v>
+        <v>46137.35423375042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
